--- a/data/processed/recorrencias.xlsx
+++ b/data/processed/recorrencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="100">
   <si>
     <t>evento</t>
   </si>
@@ -52,6 +52,9 @@
     <t>32039_2026-09-12</t>
   </si>
   <si>
+    <t>32038_2026-09-14</t>
+  </si>
+  <si>
     <t>32062_2026-09-14</t>
   </si>
   <si>
@@ -61,18 +64,36 @@
     <t>51022_2026-09-14</t>
   </si>
   <si>
+    <t>52124_2026-09-14</t>
+  </si>
+  <si>
     <t>31182_2026-09-15</t>
   </si>
   <si>
     <t>31299_2026-09-15</t>
   </si>
   <si>
+    <t>73932_2026-09-15</t>
+  </si>
+  <si>
     <t>11044_2026-09-16</t>
   </si>
   <si>
+    <t>11068_2026-09-16</t>
+  </si>
+  <si>
+    <t>11109_2026-09-16</t>
+  </si>
+  <si>
+    <t>31210_2026-09-16</t>
+  </si>
+  <si>
     <t>31503_2026-09-16</t>
   </si>
   <si>
+    <t>31615_2026-09-16</t>
+  </si>
+  <si>
     <t>31622_2026-09-16</t>
   </si>
   <si>
@@ -82,9 +103,15 @@
     <t>31818_2026-09-16</t>
   </si>
   <si>
+    <t>31844_2026-09-16</t>
+  </si>
+  <si>
     <t>31964_2026-09-16</t>
   </si>
   <si>
+    <t>31973_2026-09-16</t>
+  </si>
+  <si>
     <t>31980_2026-09-16</t>
   </si>
   <si>
@@ -94,12 +121,21 @@
     <t>51057_2026-09-16</t>
   </si>
   <si>
+    <t>52932_2026-09-16</t>
+  </si>
+  <si>
     <t>52936_2026-09-16</t>
   </si>
   <si>
+    <t>61316_2026-09-16</t>
+  </si>
+  <si>
     <t>61327_2026-09-16</t>
   </si>
   <si>
+    <t>61511_2026-09-16</t>
+  </si>
+  <si>
     <t>73362_2026-09-16</t>
   </si>
   <si>
@@ -112,6 +148,27 @@
     <t>31972_2026-09-17</t>
   </si>
   <si>
+    <t>32091_2026-09-17</t>
+  </si>
+  <si>
+    <t>51132_2026-09-17</t>
+  </si>
+  <si>
+    <t>51133_2026-09-17</t>
+  </si>
+  <si>
+    <t>52042_2026-09-17</t>
+  </si>
+  <si>
+    <t>52055_2026-09-17</t>
+  </si>
+  <si>
+    <t>61334_2026-09-17</t>
+  </si>
+  <si>
+    <t>31262_2026-09-18</t>
+  </si>
+  <si>
     <t>52104_2026-09-18</t>
   </si>
   <si>
@@ -121,21 +178,72 @@
     <t>52796_2026-09-18</t>
   </si>
   <si>
+    <t>11884_2026-09-19</t>
+  </si>
+  <si>
     <t>31165_2026-09-19</t>
   </si>
   <si>
+    <t>51060_2026-09-19</t>
+  </si>
+  <si>
     <t>51121_2026-09-19</t>
   </si>
   <si>
     <t>61766_2026-09-20</t>
   </si>
   <si>
+    <t>31120_2026-09-21</t>
+  </si>
+  <si>
     <t>61589_2026-09-21</t>
   </si>
   <si>
+    <t>61793_2026-09-21</t>
+  </si>
+  <si>
+    <t>11072_2026-09-22</t>
+  </si>
+  <si>
+    <t>11796_2026-09-22</t>
+  </si>
+  <si>
     <t>31927_2026-09-22</t>
   </si>
   <si>
+    <t>52782_2026-09-22</t>
+  </si>
+  <si>
+    <t>31738_2026-09-23</t>
+  </si>
+  <si>
+    <t>31763_2026-09-23</t>
+  </si>
+  <si>
+    <t>31795_2026-09-23</t>
+  </si>
+  <si>
+    <t>51218_2026-09-23</t>
+  </si>
+  <si>
+    <t>52139_2026-09-23</t>
+  </si>
+  <si>
+    <t>52752_2026-09-23</t>
+  </si>
+  <si>
+    <t>52828_2026-09-23</t>
+  </si>
+  <si>
+    <t>52923_2026-09-23</t>
+  </si>
+  <si>
+    <t>61350_2026-09-23</t>
+  </si>
+  <si>
+    <t>31652_2026-09-24</t>
+  </si>
+  <si>
     <t>2026-09-11</t>
   </si>
   <si>
@@ -169,16 +277,19 @@
     <t>2026-09-22</t>
   </si>
   <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
     <t>RECORRÊNCIA NA MESMA CÂMERA</t>
   </si>
   <si>
     <t>NOVO PROBLEMA EM OUTRA CÂMERA (não é recorrência)</t>
   </si>
   <si>
-    <t>2026-09-23</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
+    <t>2026-10-06</t>
   </si>
   <si>
     <t>FRONTAL (câm 21)</t>
@@ -193,10 +304,10 @@
     <t>CORREDOR 4 (câm 26)</t>
   </si>
   <si>
+    <t>FRENTE (câm 22)</t>
+  </si>
+  <si>
     <t>CORREDOR 3 (câm 25)</t>
-  </si>
-  <si>
-    <t>FRENTE (câm 22)</t>
   </si>
   <si>
     <t>OFFLINE</t>
@@ -534,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -568,19 +679,19 @@
         <v>31005</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -591,19 +702,19 @@
         <v>31093</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -614,19 +725,19 @@
         <v>31093</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="G4" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -637,19 +748,19 @@
         <v>31093</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="G5" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -660,19 +771,19 @@
         <v>31590</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -683,19 +794,19 @@
         <v>32960</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -706,19 +817,19 @@
         <v>32960</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -729,19 +840,19 @@
         <v>32039</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -749,68 +860,68 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>32062</v>
+        <v>32038</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="G10" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11">
-        <v>32616</v>
+        <v>32038</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>51022</v>
+        <v>32062</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="G12" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -818,22 +929,22 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>51022</v>
+        <v>32616</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="G13" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -841,22 +952,22 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>31182</v>
+        <v>51022</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="G14" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -864,22 +975,22 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>31182</v>
+        <v>51022</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -887,45 +998,45 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>31299</v>
+        <v>52124</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17">
-        <v>31299</v>
+        <v>31182</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="G17" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -933,22 +1044,22 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>11044</v>
+        <v>31182</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G18" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -956,367 +1067,367 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>31503</v>
+        <v>31299</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>31622</v>
+        <v>31299</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="G20" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21">
-        <v>31755</v>
+        <v>73932</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="G21" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22">
-        <v>31818</v>
+        <v>11044</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="G22" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23">
-        <v>31964</v>
+        <v>11068</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="G23" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24">
-        <v>31980</v>
+        <v>11109</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25">
-        <v>31984</v>
+        <v>31210</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="G25" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26">
-        <v>51057</v>
+        <v>31503</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="G26" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27">
-        <v>52936</v>
+        <v>31615</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="G27" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28">
-        <v>61327</v>
+        <v>31622</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29">
-        <v>73362</v>
+        <v>31755</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30">
-        <v>11695</v>
+        <v>31818</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F30" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="G30" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31">
-        <v>31180</v>
+        <v>31844</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E31" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="G31" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32">
-        <v>31972</v>
+        <v>31844</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="E32" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33">
-        <v>52104</v>
+        <v>31964</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E33" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="G33" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34">
-        <v>52104</v>
+        <v>31973</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E34" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1324,22 +1435,22 @@
         <v>32</v>
       </c>
       <c r="B35">
-        <v>52104</v>
+        <v>31980</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E35" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="F35" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1347,22 +1458,22 @@
         <v>33</v>
       </c>
       <c r="B36">
-        <v>52749</v>
+        <v>31984</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="G36" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1370,275 +1481,1425 @@
         <v>34</v>
       </c>
       <c r="B37">
-        <v>52796</v>
+        <v>51057</v>
       </c>
       <c r="C37" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="E37" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="G37" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B38">
-        <v>52796</v>
+        <v>52932</v>
       </c>
       <c r="C38" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="F38" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="G38" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39">
-        <v>31165</v>
+        <v>52936</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E39" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B40">
-        <v>51121</v>
+        <v>61316</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="F40" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="G40" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41">
-        <v>61766</v>
+        <v>61327</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E41" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F41" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B42">
-        <v>61766</v>
+        <v>61511</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D42" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="F42" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B43">
-        <v>61766</v>
+        <v>73362</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D43" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="F43" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="G43" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B44">
-        <v>61766</v>
+        <v>73362</v>
       </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E44" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="F44" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="G44" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B45">
-        <v>61766</v>
+        <v>11695</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F45" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="G45" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B46">
-        <v>61589</v>
+        <v>31180</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E46" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="F46" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="G46" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B47">
-        <v>31927</v>
+        <v>31972</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E47" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="F47" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="G47" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B48">
+        <v>32091</v>
+      </c>
+      <c r="C48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" t="s">
+        <v>89</v>
+      </c>
+      <c r="E48" t="s">
+        <v>91</v>
+      </c>
+      <c r="F48" t="s">
+        <v>92</v>
+      </c>
+      <c r="G48" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49">
+        <v>51132</v>
+      </c>
+      <c r="C49" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" t="s">
+        <v>90</v>
+      </c>
+      <c r="E49" t="s">
+        <v>91</v>
+      </c>
+      <c r="F49" t="s">
+        <v>96</v>
+      </c>
+      <c r="G49" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50">
+        <v>51133</v>
+      </c>
+      <c r="C50" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" t="s">
+        <v>91</v>
+      </c>
+      <c r="F50" t="s">
+        <v>96</v>
+      </c>
+      <c r="G50" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>47</v>
+      </c>
+      <c r="B51">
+        <v>52042</v>
+      </c>
+      <c r="C51" t="s">
+        <v>81</v>
+      </c>
+      <c r="D51" t="s">
+        <v>90</v>
+      </c>
+      <c r="E51" t="s">
+        <v>91</v>
+      </c>
+      <c r="F51" t="s">
+        <v>96</v>
+      </c>
+      <c r="G51" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52">
+        <v>52055</v>
+      </c>
+      <c r="C52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D52" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52" t="s">
+        <v>92</v>
+      </c>
+      <c r="G52" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>49</v>
+      </c>
+      <c r="B53">
+        <v>61334</v>
+      </c>
+      <c r="C53" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" t="s">
+        <v>89</v>
+      </c>
+      <c r="E53" t="s">
+        <v>91</v>
+      </c>
+      <c r="F53" t="s">
+        <v>94</v>
+      </c>
+      <c r="G53" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>50</v>
+      </c>
+      <c r="B54">
+        <v>31262</v>
+      </c>
+      <c r="C54" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" t="s">
+        <v>90</v>
+      </c>
+      <c r="E54" t="s">
+        <v>91</v>
+      </c>
+      <c r="F54" t="s">
+        <v>96</v>
+      </c>
+      <c r="G54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>51</v>
+      </c>
+      <c r="B55">
+        <v>52104</v>
+      </c>
+      <c r="C55" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" t="s">
+        <v>90</v>
+      </c>
+      <c r="E55" t="s">
+        <v>86</v>
+      </c>
+      <c r="F55" t="s">
+        <v>92</v>
+      </c>
+      <c r="G55" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>51</v>
+      </c>
+      <c r="B56">
+        <v>52104</v>
+      </c>
+      <c r="C56" t="s">
+        <v>82</v>
+      </c>
+      <c r="D56" t="s">
+        <v>90</v>
+      </c>
+      <c r="E56" t="s">
+        <v>86</v>
+      </c>
+      <c r="F56" t="s">
+        <v>93</v>
+      </c>
+      <c r="G56" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>51</v>
+      </c>
+      <c r="B57">
+        <v>52104</v>
+      </c>
+      <c r="C57" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" t="s">
+        <v>90</v>
+      </c>
+      <c r="E57" t="s">
+        <v>86</v>
+      </c>
+      <c r="F57" t="s">
+        <v>97</v>
+      </c>
+      <c r="G57" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>52</v>
+      </c>
+      <c r="B58">
+        <v>52749</v>
+      </c>
+      <c r="C58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58" t="s">
+        <v>89</v>
+      </c>
+      <c r="E58" t="s">
+        <v>87</v>
+      </c>
+      <c r="F58" t="s">
+        <v>94</v>
+      </c>
+      <c r="G58" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>52</v>
+      </c>
+      <c r="B59">
+        <v>52749</v>
+      </c>
+      <c r="C59" t="s">
+        <v>82</v>
+      </c>
+      <c r="D59" t="s">
+        <v>90</v>
+      </c>
+      <c r="E59" t="s">
+        <v>91</v>
+      </c>
+      <c r="F59" t="s">
+        <v>92</v>
+      </c>
+      <c r="G59" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>53</v>
+      </c>
+      <c r="B60">
+        <v>52796</v>
+      </c>
+      <c r="C60" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" t="s">
+        <v>89</v>
+      </c>
+      <c r="E60" t="s">
+        <v>88</v>
+      </c>
+      <c r="F60" t="s">
+        <v>93</v>
+      </c>
+      <c r="G60" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>53</v>
+      </c>
+      <c r="B61">
+        <v>52796</v>
+      </c>
+      <c r="C61" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" t="s">
+        <v>90</v>
+      </c>
+      <c r="E61" t="s">
+        <v>88</v>
+      </c>
+      <c r="F61" t="s">
+        <v>96</v>
+      </c>
+      <c r="G61" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>54</v>
+      </c>
+      <c r="B62">
+        <v>11884</v>
+      </c>
+      <c r="C62" t="s">
+        <v>83</v>
+      </c>
+      <c r="D62" t="s">
+        <v>90</v>
+      </c>
+      <c r="E62" t="s">
+        <v>91</v>
+      </c>
+      <c r="F62" t="s">
+        <v>93</v>
+      </c>
+      <c r="G62" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63">
+        <v>31165</v>
+      </c>
+      <c r="C63" t="s">
+        <v>83</v>
+      </c>
+      <c r="D63" t="s">
+        <v>90</v>
+      </c>
+      <c r="E63" t="s">
+        <v>85</v>
+      </c>
+      <c r="F63" t="s">
+        <v>94</v>
+      </c>
+      <c r="G63" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64">
+        <v>51060</v>
+      </c>
+      <c r="C64" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64" t="s">
+        <v>90</v>
+      </c>
+      <c r="E64" t="s">
+        <v>91</v>
+      </c>
+      <c r="F64" t="s">
+        <v>96</v>
+      </c>
+      <c r="G64" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>57</v>
+      </c>
+      <c r="B65">
+        <v>51121</v>
+      </c>
+      <c r="C65" t="s">
+        <v>83</v>
+      </c>
+      <c r="D65" t="s">
+        <v>90</v>
+      </c>
+      <c r="E65" t="s">
+        <v>85</v>
+      </c>
+      <c r="F65" t="s">
+        <v>92</v>
+      </c>
+      <c r="G65" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>58</v>
+      </c>
+      <c r="B66">
+        <v>61766</v>
+      </c>
+      <c r="C66" t="s">
+        <v>84</v>
+      </c>
+      <c r="D66" t="s">
+        <v>90</v>
+      </c>
+      <c r="E66" t="s">
+        <v>85</v>
+      </c>
+      <c r="F66" t="s">
+        <v>92</v>
+      </c>
+      <c r="G66" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>58</v>
+      </c>
+      <c r="B67">
+        <v>61766</v>
+      </c>
+      <c r="C67" t="s">
+        <v>84</v>
+      </c>
+      <c r="D67" t="s">
+        <v>90</v>
+      </c>
+      <c r="E67" t="s">
+        <v>85</v>
+      </c>
+      <c r="F67" t="s">
+        <v>96</v>
+      </c>
+      <c r="G67" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>58</v>
+      </c>
+      <c r="B68">
+        <v>61766</v>
+      </c>
+      <c r="C68" t="s">
+        <v>84</v>
+      </c>
+      <c r="D68" t="s">
+        <v>90</v>
+      </c>
+      <c r="E68" t="s">
+        <v>85</v>
+      </c>
+      <c r="F68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G68" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69">
+        <v>61766</v>
+      </c>
+      <c r="C69" t="s">
+        <v>84</v>
+      </c>
+      <c r="D69" t="s">
+        <v>90</v>
+      </c>
+      <c r="E69" t="s">
+        <v>85</v>
+      </c>
+      <c r="F69" t="s">
+        <v>94</v>
+      </c>
+      <c r="G69" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70">
+        <v>61766</v>
+      </c>
+      <c r="C70" t="s">
+        <v>84</v>
+      </c>
+      <c r="D70" t="s">
+        <v>90</v>
+      </c>
+      <c r="E70" t="s">
+        <v>85</v>
+      </c>
+      <c r="F70" t="s">
+        <v>97</v>
+      </c>
+      <c r="G70" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71">
+        <v>31120</v>
+      </c>
+      <c r="C71" t="s">
+        <v>85</v>
+      </c>
+      <c r="D71" t="s">
+        <v>89</v>
+      </c>
+      <c r="E71" t="s">
+        <v>91</v>
+      </c>
+      <c r="F71" t="s">
+        <v>94</v>
+      </c>
+      <c r="G71" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>60</v>
+      </c>
+      <c r="B72">
+        <v>61589</v>
+      </c>
+      <c r="C72" t="s">
+        <v>85</v>
+      </c>
+      <c r="D72" t="s">
+        <v>90</v>
+      </c>
+      <c r="E72" t="s">
+        <v>86</v>
+      </c>
+      <c r="F72" t="s">
+        <v>94</v>
+      </c>
+      <c r="G72" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73">
+        <v>61793</v>
+      </c>
+      <c r="C73" t="s">
+        <v>85</v>
+      </c>
+      <c r="D73" t="s">
+        <v>89</v>
+      </c>
+      <c r="E73" t="s">
+        <v>91</v>
+      </c>
+      <c r="F73" t="s">
+        <v>92</v>
+      </c>
+      <c r="G73" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74">
+        <v>61793</v>
+      </c>
+      <c r="C74" t="s">
+        <v>85</v>
+      </c>
+      <c r="D74" t="s">
+        <v>89</v>
+      </c>
+      <c r="E74" t="s">
+        <v>91</v>
+      </c>
+      <c r="F74" t="s">
+        <v>96</v>
+      </c>
+      <c r="G74" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75">
+        <v>61793</v>
+      </c>
+      <c r="C75" t="s">
+        <v>85</v>
+      </c>
+      <c r="D75" t="s">
+        <v>89</v>
+      </c>
+      <c r="E75" t="s">
+        <v>91</v>
+      </c>
+      <c r="F75" t="s">
+        <v>94</v>
+      </c>
+      <c r="G75" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>61</v>
+      </c>
+      <c r="B76">
+        <v>61793</v>
+      </c>
+      <c r="C76" t="s">
+        <v>85</v>
+      </c>
+      <c r="D76" t="s">
+        <v>89</v>
+      </c>
+      <c r="E76" t="s">
+        <v>91</v>
+      </c>
+      <c r="F76" t="s">
+        <v>97</v>
+      </c>
+      <c r="G76" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77">
+        <v>11072</v>
+      </c>
+      <c r="C77" t="s">
+        <v>86</v>
+      </c>
+      <c r="D77" t="s">
+        <v>89</v>
+      </c>
+      <c r="E77" t="s">
+        <v>91</v>
+      </c>
+      <c r="F77" t="s">
+        <v>95</v>
+      </c>
+      <c r="G77" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78">
+        <v>11796</v>
+      </c>
+      <c r="C78" t="s">
+        <v>86</v>
+      </c>
+      <c r="D78" t="s">
+        <v>89</v>
+      </c>
+      <c r="E78" t="s">
+        <v>91</v>
+      </c>
+      <c r="F78" t="s">
+        <v>93</v>
+      </c>
+      <c r="G78" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79">
         <v>31927</v>
       </c>
-      <c r="C48" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" t="s">
-        <v>52</v>
-      </c>
-      <c r="E48" t="s">
-        <v>53</v>
-      </c>
-      <c r="F48" t="s">
-        <v>58</v>
-      </c>
-      <c r="G48" t="s">
-        <v>62</v>
+      <c r="C79" t="s">
+        <v>86</v>
+      </c>
+      <c r="D79" t="s">
+        <v>90</v>
+      </c>
+      <c r="E79" t="s">
+        <v>87</v>
+      </c>
+      <c r="F79" t="s">
+        <v>97</v>
+      </c>
+      <c r="G79" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>64</v>
+      </c>
+      <c r="B80">
+        <v>31927</v>
+      </c>
+      <c r="C80" t="s">
+        <v>86</v>
+      </c>
+      <c r="D80" t="s">
+        <v>90</v>
+      </c>
+      <c r="E80" t="s">
+        <v>87</v>
+      </c>
+      <c r="F80" t="s">
+        <v>95</v>
+      </c>
+      <c r="G80" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81">
+        <v>52782</v>
+      </c>
+      <c r="C81" t="s">
+        <v>86</v>
+      </c>
+      <c r="D81" t="s">
+        <v>89</v>
+      </c>
+      <c r="E81" t="s">
+        <v>91</v>
+      </c>
+      <c r="F81" t="s">
+        <v>97</v>
+      </c>
+      <c r="G81" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>66</v>
+      </c>
+      <c r="B82">
+        <v>31738</v>
+      </c>
+      <c r="C82" t="s">
+        <v>87</v>
+      </c>
+      <c r="D82" t="s">
+        <v>90</v>
+      </c>
+      <c r="E82" t="s">
+        <v>91</v>
+      </c>
+      <c r="F82" t="s">
+        <v>96</v>
+      </c>
+      <c r="G82" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>67</v>
+      </c>
+      <c r="B83">
+        <v>31763</v>
+      </c>
+      <c r="C83" t="s">
+        <v>87</v>
+      </c>
+      <c r="D83" t="s">
+        <v>89</v>
+      </c>
+      <c r="E83" t="s">
+        <v>91</v>
+      </c>
+      <c r="F83" t="s">
+        <v>92</v>
+      </c>
+      <c r="G83" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>67</v>
+      </c>
+      <c r="B84">
+        <v>31763</v>
+      </c>
+      <c r="C84" t="s">
+        <v>87</v>
+      </c>
+      <c r="D84" t="s">
+        <v>90</v>
+      </c>
+      <c r="E84" t="s">
+        <v>91</v>
+      </c>
+      <c r="F84" t="s">
+        <v>96</v>
+      </c>
+      <c r="G84" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>68</v>
+      </c>
+      <c r="B85">
+        <v>31795</v>
+      </c>
+      <c r="C85" t="s">
+        <v>87</v>
+      </c>
+      <c r="D85" t="s">
+        <v>90</v>
+      </c>
+      <c r="E85" t="s">
+        <v>91</v>
+      </c>
+      <c r="F85" t="s">
+        <v>92</v>
+      </c>
+      <c r="G85" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" t="s">
+        <v>68</v>
+      </c>
+      <c r="B86">
+        <v>31795</v>
+      </c>
+      <c r="C86" t="s">
+        <v>87</v>
+      </c>
+      <c r="D86" t="s">
+        <v>90</v>
+      </c>
+      <c r="E86" t="s">
+        <v>91</v>
+      </c>
+      <c r="F86" t="s">
+        <v>96</v>
+      </c>
+      <c r="G86" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>69</v>
+      </c>
+      <c r="B87">
+        <v>51218</v>
+      </c>
+      <c r="C87" t="s">
+        <v>87</v>
+      </c>
+      <c r="D87" t="s">
+        <v>90</v>
+      </c>
+      <c r="E87" t="s">
+        <v>91</v>
+      </c>
+      <c r="F87" t="s">
+        <v>96</v>
+      </c>
+      <c r="G87" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>70</v>
+      </c>
+      <c r="B88">
+        <v>52139</v>
+      </c>
+      <c r="C88" t="s">
+        <v>87</v>
+      </c>
+      <c r="D88" t="s">
+        <v>90</v>
+      </c>
+      <c r="E88" t="s">
+        <v>91</v>
+      </c>
+      <c r="F88" t="s">
+        <v>96</v>
+      </c>
+      <c r="G88" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>71</v>
+      </c>
+      <c r="B89">
+        <v>52752</v>
+      </c>
+      <c r="C89" t="s">
+        <v>87</v>
+      </c>
+      <c r="D89" t="s">
+        <v>89</v>
+      </c>
+      <c r="E89" t="s">
+        <v>91</v>
+      </c>
+      <c r="F89" t="s">
+        <v>95</v>
+      </c>
+      <c r="G89" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>71</v>
+      </c>
+      <c r="B90">
+        <v>52752</v>
+      </c>
+      <c r="C90" t="s">
+        <v>87</v>
+      </c>
+      <c r="D90" t="s">
+        <v>90</v>
+      </c>
+      <c r="E90" t="s">
+        <v>91</v>
+      </c>
+      <c r="F90" t="s">
+        <v>92</v>
+      </c>
+      <c r="G90" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>71</v>
+      </c>
+      <c r="B91">
+        <v>52752</v>
+      </c>
+      <c r="C91" t="s">
+        <v>87</v>
+      </c>
+      <c r="D91" t="s">
+        <v>90</v>
+      </c>
+      <c r="E91" t="s">
+        <v>91</v>
+      </c>
+      <c r="F91" t="s">
+        <v>96</v>
+      </c>
+      <c r="G91" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>71</v>
+      </c>
+      <c r="B92">
+        <v>52752</v>
+      </c>
+      <c r="C92" t="s">
+        <v>87</v>
+      </c>
+      <c r="D92" t="s">
+        <v>90</v>
+      </c>
+      <c r="E92" t="s">
+        <v>91</v>
+      </c>
+      <c r="F92" t="s">
+        <v>93</v>
+      </c>
+      <c r="G92" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>71</v>
+      </c>
+      <c r="B93">
+        <v>52752</v>
+      </c>
+      <c r="C93" t="s">
+        <v>87</v>
+      </c>
+      <c r="D93" t="s">
+        <v>90</v>
+      </c>
+      <c r="E93" t="s">
+        <v>91</v>
+      </c>
+      <c r="F93" t="s">
+        <v>94</v>
+      </c>
+      <c r="G93" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>71</v>
+      </c>
+      <c r="B94">
+        <v>52752</v>
+      </c>
+      <c r="C94" t="s">
+        <v>87</v>
+      </c>
+      <c r="D94" t="s">
+        <v>90</v>
+      </c>
+      <c r="E94" t="s">
+        <v>91</v>
+      </c>
+      <c r="F94" t="s">
+        <v>97</v>
+      </c>
+      <c r="G94" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>72</v>
+      </c>
+      <c r="B95">
+        <v>52828</v>
+      </c>
+      <c r="C95" t="s">
+        <v>87</v>
+      </c>
+      <c r="D95" t="s">
+        <v>89</v>
+      </c>
+      <c r="E95" t="s">
+        <v>91</v>
+      </c>
+      <c r="F95" t="s">
+        <v>96</v>
+      </c>
+      <c r="G95" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>73</v>
+      </c>
+      <c r="B96">
+        <v>52923</v>
+      </c>
+      <c r="C96" t="s">
+        <v>87</v>
+      </c>
+      <c r="D96" t="s">
+        <v>90</v>
+      </c>
+      <c r="E96" t="s">
+        <v>91</v>
+      </c>
+      <c r="F96" t="s">
+        <v>96</v>
+      </c>
+      <c r="G96" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>74</v>
+      </c>
+      <c r="B97">
+        <v>61350</v>
+      </c>
+      <c r="C97" t="s">
+        <v>87</v>
+      </c>
+      <c r="D97" t="s">
+        <v>90</v>
+      </c>
+      <c r="E97" t="s">
+        <v>91</v>
+      </c>
+      <c r="F97" t="s">
+        <v>96</v>
+      </c>
+      <c r="G97" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>75</v>
+      </c>
+      <c r="B98">
+        <v>31652</v>
+      </c>
+      <c r="C98" t="s">
+        <v>88</v>
+      </c>
+      <c r="D98" t="s">
+        <v>90</v>
+      </c>
+      <c r="E98" t="s">
+        <v>91</v>
+      </c>
+      <c r="F98" t="s">
+        <v>93</v>
+      </c>
+      <c r="G98" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
